--- a/output/第10期計画_中間報告会議議事録の校正結果_第2回.xlsx
+++ b/output/第10期計画_中間報告会議議事録の校正結果_第2回.xlsx
@@ -1387,14 +1387,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ご提案（3件・本文は変えていません）</t>
+          <t>ご提案（3件・本文へ反映済み）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>発注者が意図して編集された箇所に関わるため、受託者の判断では変えず、ご意向を伺うものです。ご指示をいただければ反映いたします。</t>
+          <t>発注者が意図して編集された箇所に関わるため、当初はご意向を伺うにとどめていたものです。ご決定をお待ちしている間の扱いとして、ご提案のとおり本文へ反映しました。</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>現行（受領版2のまま）</t>
+          <t>受領版2の表記</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ご提案</t>
+          <t>ご提案（反映後の表記）</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1523,9 +1523,9 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>注1）3件とも、発注者が意図して編集された箇所に関わります。受託者の判断で戻すことはせず、ご意向を伺います。
+          <t>注1）3件とも、発注者が意図して編集された箇所に関わります。ご決定をお待ちしている間の扱いとして反映したものであり、受領版2の表記のままとするご判断であれば戻します。
 注2）いずれも文意は変わりません。読みやすさと文体の統一に関するものです。
-注3）このままで差し支えないとのご判断であれば、受領版2の表記のままで確定します。</t>
+注3）反映した3件は、本文の該当箇所がご提案のとおりの表記になっていることを確かめています。</t>
         </is>
       </c>
     </row>
